--- a/Complete_LOG.xlsx
+++ b/Complete_LOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EE211-AE28-4670-929C-9C7E3544BDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82EC5F-35AD-4477-84F2-5E33D3102494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
   <si>
     <t>Training data folder</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Model Time</t>
   </si>
   <si>
-    <t>I=11</t>
-  </si>
-  <si>
     <t>D=1</t>
   </si>
   <si>
@@ -166,6 +163,21 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>Material PR</t>
+  </si>
+  <si>
+    <t>Material DU</t>
+  </si>
+  <si>
+    <t>I=12</t>
+  </si>
+  <si>
+    <t>Databse</t>
+  </si>
+  <si>
+    <t>Subset of 1001</t>
   </si>
 </sst>
 </file>
@@ -194,7 +206,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,6 +231,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -232,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -263,6 +281,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8928FC43-EDFC-4E42-BD9C-B150B86ED97F}">
-  <dimension ref="A2:T26"/>
+  <dimension ref="A2:T29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.85546875" customWidth="1"/>
@@ -630,10 +663,10 @@
         <v>14</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>12</v>
@@ -680,14 +713,14 @@
       <c r="O3" s="2">
         <v>101</v>
       </c>
-      <c r="P3" s="10" t="s">
-        <v>20</v>
+      <c r="P3" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="Q3" s="1">
         <v>1</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -727,12 +760,12 @@
       <c r="O4" s="2">
         <v>102</v>
       </c>
-      <c r="P4" s="10"/>
+      <c r="P4" s="14"/>
       <c r="Q4" s="1">
         <v>1.5</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>18</v>
+      <c r="R4" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -772,12 +805,12 @@
       <c r="O5" s="2">
         <v>103</v>
       </c>
-      <c r="P5" s="10"/>
+      <c r="P5" s="14"/>
       <c r="Q5" s="1">
         <v>2</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>18</v>
+      <c r="R5" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -817,12 +850,12 @@
       <c r="O6" s="2">
         <v>104</v>
       </c>
-      <c r="P6" s="10"/>
+      <c r="P6" s="14"/>
       <c r="Q6" s="1">
         <v>3</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>18</v>
+      <c r="R6" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -864,20 +897,20 @@
       <c r="O7" s="4">
         <v>201</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="1">
         <v>11</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>18</v>
+      <c r="R7" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S7" s="1">
         <v>6</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
@@ -917,12 +950,12 @@
       <c r="O8" s="4">
         <v>202</v>
       </c>
-      <c r="P8" s="10"/>
+      <c r="P8" s="14"/>
       <c r="Q8" s="1">
         <v>20</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>18</v>
+      <c r="R8" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S8" s="1">
         <v>22</v>
@@ -966,12 +999,12 @@
       <c r="O9" s="4">
         <v>203</v>
       </c>
-      <c r="P9" s="10"/>
+      <c r="P9" s="14"/>
       <c r="Q9" s="1">
         <v>31</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>18</v>
+      <c r="R9" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S9" s="1">
         <v>130</v>
@@ -991,7 +1024,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1015,12 +1048,12 @@
       <c r="O10" s="4">
         <v>204</v>
       </c>
-      <c r="P10" s="10"/>
+      <c r="P10" s="14"/>
       <c r="Q10" s="1">
         <v>45</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>18</v>
+      <c r="R10" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="S10" s="1">
         <v>350</v>
@@ -1040,7 +1073,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1">
         <v>10</v>
@@ -1056,7 +1089,7 @@
         <v>21</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="3">
@@ -1066,14 +1099,14 @@
       <c r="O11" s="4">
         <v>301</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="14" t="s">
         <v>15</v>
       </c>
       <c r="Q11" s="1">
         <v>11</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S11" s="1">
         <v>6</v>
@@ -1093,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1">
         <v>10</v>
@@ -1113,12 +1146,12 @@
       <c r="O12" s="4">
         <v>302</v>
       </c>
-      <c r="P12" s="10"/>
+      <c r="P12" s="14"/>
       <c r="Q12" s="1">
         <v>20</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S12" s="1">
         <v>22</v>
@@ -1138,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1">
         <v>10</v>
@@ -1158,12 +1191,12 @@
       <c r="O13" s="4">
         <v>303</v>
       </c>
-      <c r="P13" s="10"/>
+      <c r="P13" s="14"/>
       <c r="Q13" s="1">
         <v>31</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S13" s="1">
         <v>130</v>
@@ -1180,10 +1213,10 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1203,12 +1236,12 @@
       <c r="O14" s="4">
         <v>304</v>
       </c>
-      <c r="P14" s="10"/>
+      <c r="P14" s="14"/>
       <c r="Q14" s="1">
         <v>45</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S14" s="1">
         <v>350</v>
@@ -1225,10 +1258,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1248,14 +1281,14 @@
       <c r="O15" s="2">
         <v>401</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>20</v>
+      <c r="P15" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="Q15" s="1">
         <v>1</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1268,10 +1301,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -1291,12 +1324,12 @@
       <c r="O16" s="2">
         <v>402</v>
       </c>
-      <c r="P16" s="10"/>
+      <c r="P16" s="14"/>
       <c r="Q16" s="1">
         <v>1.5</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1309,10 +1342,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -1332,19 +1365,19 @@
       <c r="O17" s="2">
         <v>403</v>
       </c>
-      <c r="P17" s="10"/>
+      <c r="P17" s="14"/>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>38</v>
+      <c r="A18" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="B18" s="1">
         <v>201</v>
@@ -1353,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -1376,18 +1409,18 @@
       <c r="O18" s="2">
         <v>404</v>
       </c>
-      <c r="P18" s="10"/>
+      <c r="P18" s="14"/>
       <c r="Q18" s="1">
         <v>3</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="8">
         <v>202</v>
       </c>
@@ -1395,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -1409,9 +1442,21 @@
       <c r="H19" s="8">
         <v>1</v>
       </c>
+      <c r="O19" s="12">
+        <v>501</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>5</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="8">
         <v>203</v>
       </c>
@@ -1419,10 +1464,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="8">
         <v>1</v>
@@ -1433,9 +1478,19 @@
       <c r="H20" s="8">
         <v>1</v>
       </c>
+      <c r="O20" s="12">
+        <v>502</v>
+      </c>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="10">
+        <v>10</v>
+      </c>
+      <c r="R20" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="8">
         <v>204</v>
       </c>
@@ -1443,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="8">
         <v>1</v>
@@ -1457,10 +1512,20 @@
       <c r="H21" s="8">
         <v>1</v>
       </c>
+      <c r="O21" s="12">
+        <v>503</v>
+      </c>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="10">
+        <v>20</v>
+      </c>
+      <c r="R21" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>39</v>
+      <c r="A22" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="B22" s="8">
         <v>301</v>
@@ -1469,11 +1534,11 @@
         <v>1</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="F22" s="8">
         <v>1</v>
       </c>
@@ -1483,9 +1548,19 @@
       <c r="H22" s="8">
         <v>1</v>
       </c>
+      <c r="O22" s="12">
+        <v>504</v>
+      </c>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="10">
+        <v>30</v>
+      </c>
+      <c r="R22" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="8">
         <v>302</v>
       </c>
@@ -1493,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" s="8">
         <v>1</v>
@@ -1507,9 +1582,21 @@
       <c r="H23" s="8">
         <v>1</v>
       </c>
+      <c r="O23" s="12">
+        <v>601</v>
+      </c>
+      <c r="P23" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>5</v>
+      </c>
+      <c r="R23" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="8">
         <v>303</v>
       </c>
@@ -1517,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" s="8">
         <v>1</v>
@@ -1531,9 +1618,19 @@
       <c r="H24" s="8">
         <v>1</v>
       </c>
+      <c r="O24" s="12">
+        <v>602</v>
+      </c>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="11">
+        <v>10</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="8">
         <v>304</v>
       </c>
@@ -1541,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" s="8">
         <v>1</v>
@@ -1554,26 +1651,124 @@
       </c>
       <c r="H25" s="8">
         <v>1</v>
+      </c>
+      <c r="O25" s="12">
+        <v>603</v>
+      </c>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="11">
+        <v>20</v>
+      </c>
+      <c r="R25" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="9">
         <v>402</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="C26" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="O26" s="12">
+        <v>604</v>
+      </c>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="11">
+        <v>30</v>
+      </c>
+      <c r="R26" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="13">
+        <v>1001</v>
+      </c>
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="13">
+        <v>90</v>
+      </c>
+      <c r="G27" s="13">
+        <v>10</v>
+      </c>
+      <c r="H27" s="13">
+        <v>900</v>
+      </c>
+      <c r="J27" s="13">
+        <v>1001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+      <c r="B28" s="13">
+        <v>1002</v>
+      </c>
+      <c r="C28" s="13">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="13">
+        <v>300</v>
+      </c>
+      <c r="J28">
+        <v>1002</v>
+      </c>
+      <c r="K28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="13">
+        <v>1003</v>
+      </c>
+      <c r="C29" s="13">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="13">
+        <v>100</v>
+      </c>
+      <c r="J29">
+        <v>1003</v>
+      </c>
+      <c r="K29" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A27:A29"/>
     <mergeCell ref="P3:P6"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="C26:H26"/>
@@ -1581,6 +1776,8 @@
     <mergeCell ref="P7:P10"/>
     <mergeCell ref="P11:P14"/>
     <mergeCell ref="P15:P18"/>
+    <mergeCell ref="P19:P22"/>
+    <mergeCell ref="P23:P26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Complete_LOG.xlsx
+++ b/Complete_LOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82EC5F-35AD-4477-84F2-5E33D3102494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E398691-29E0-40B1-8168-C9D265710DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
   <si>
     <t>Training data folder</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Subset of 1001</t>
+  </si>
+  <si>
+    <t>Material dist</t>
   </si>
 </sst>
 </file>
@@ -250,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,6 +289,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -611,9 +629,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8928FC43-EDFC-4E42-BD9C-B150B86ED97F}">
-  <dimension ref="A2:T29"/>
+  <dimension ref="A2:T35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
@@ -683,20 +702,20 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1">
+        <v>9</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16">
         <v>50</v>
       </c>
-      <c r="G3" s="1">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1">
-        <v>500</v>
+      <c r="G3" s="16">
+        <v>10</v>
+      </c>
+      <c r="H3" s="16">
+        <v>4500</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1">
@@ -713,7 +732,7 @@
       <c r="O3" s="2">
         <v>101</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="19" t="s">
         <v>19</v>
       </c>
       <c r="Q3" s="1">
@@ -750,7 +769,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1">
         <v>5</v>
@@ -760,7 +779,7 @@
       <c r="O4" s="2">
         <v>102</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="19"/>
       <c r="Q4" s="1">
         <v>1.5</v>
       </c>
@@ -805,7 +824,7 @@
       <c r="O5" s="2">
         <v>103</v>
       </c>
-      <c r="P5" s="14"/>
+      <c r="P5" s="19"/>
       <c r="Q5" s="1">
         <v>2</v>
       </c>
@@ -850,7 +869,7 @@
       <c r="O6" s="2">
         <v>104</v>
       </c>
-      <c r="P6" s="14"/>
+      <c r="P6" s="19"/>
       <c r="Q6" s="1">
         <v>3</v>
       </c>
@@ -897,7 +916,7 @@
       <c r="O7" s="4">
         <v>201</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="19" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="1">
@@ -950,7 +969,7 @@
       <c r="O8" s="4">
         <v>202</v>
       </c>
-      <c r="P8" s="14"/>
+      <c r="P8" s="19"/>
       <c r="Q8" s="1">
         <v>20</v>
       </c>
@@ -999,7 +1018,7 @@
       <c r="O9" s="4">
         <v>203</v>
       </c>
-      <c r="P9" s="14"/>
+      <c r="P9" s="19"/>
       <c r="Q9" s="1">
         <v>31</v>
       </c>
@@ -1048,7 +1067,7 @@
       <c r="O10" s="4">
         <v>204</v>
       </c>
-      <c r="P10" s="14"/>
+      <c r="P10" s="19"/>
       <c r="Q10" s="1">
         <v>45</v>
       </c>
@@ -1099,7 +1118,7 @@
       <c r="O11" s="4">
         <v>301</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="P11" s="19" t="s">
         <v>15</v>
       </c>
       <c r="Q11" s="1">
@@ -1146,7 +1165,7 @@
       <c r="O12" s="4">
         <v>302</v>
       </c>
-      <c r="P12" s="14"/>
+      <c r="P12" s="19"/>
       <c r="Q12" s="1">
         <v>20</v>
       </c>
@@ -1191,7 +1210,7 @@
       <c r="O13" s="4">
         <v>303</v>
       </c>
-      <c r="P13" s="14"/>
+      <c r="P13" s="19"/>
       <c r="Q13" s="1">
         <v>31</v>
       </c>
@@ -1236,7 +1255,7 @@
       <c r="O14" s="4">
         <v>304</v>
       </c>
-      <c r="P14" s="14"/>
+      <c r="P14" s="19"/>
       <c r="Q14" s="1">
         <v>45</v>
       </c>
@@ -1281,7 +1300,7 @@
       <c r="O15" s="2">
         <v>401</v>
       </c>
-      <c r="P15" s="14" t="s">
+      <c r="P15" s="19" t="s">
         <v>19</v>
       </c>
       <c r="Q15" s="1">
@@ -1324,7 +1343,7 @@
       <c r="O16" s="2">
         <v>402</v>
       </c>
-      <c r="P16" s="14"/>
+      <c r="P16" s="19"/>
       <c r="Q16" s="1">
         <v>1.5</v>
       </c>
@@ -1365,7 +1384,7 @@
       <c r="O17" s="2">
         <v>403</v>
       </c>
-      <c r="P17" s="14"/>
+      <c r="P17" s="19"/>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
@@ -1376,7 +1395,7 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1">
@@ -1409,7 +1428,7 @@
       <c r="O18" s="2">
         <v>404</v>
       </c>
-      <c r="P18" s="14"/>
+      <c r="P18" s="19"/>
       <c r="Q18" s="1">
         <v>3</v>
       </c>
@@ -1420,7 +1439,7 @@
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="8">
         <v>202</v>
       </c>
@@ -1445,7 +1464,7 @@
       <c r="O19" s="12">
         <v>501</v>
       </c>
-      <c r="P19" s="15" t="s">
+      <c r="P19" s="20" t="s">
         <v>43</v>
       </c>
       <c r="Q19" s="10">
@@ -1456,7 +1475,7 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="8">
         <v>203</v>
       </c>
@@ -1481,7 +1500,7 @@
       <c r="O20" s="12">
         <v>502</v>
       </c>
-      <c r="P20" s="15"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="10">
         <v>10</v>
       </c>
@@ -1490,7 +1509,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="8">
         <v>204</v>
       </c>
@@ -1515,7 +1534,7 @@
       <c r="O21" s="12">
         <v>503</v>
       </c>
-      <c r="P21" s="15"/>
+      <c r="P21" s="20"/>
       <c r="Q21" s="10">
         <v>20</v>
       </c>
@@ -1524,7 +1543,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="19" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="8">
@@ -1551,7 +1570,7 @@
       <c r="O22" s="12">
         <v>504</v>
       </c>
-      <c r="P22" s="15"/>
+      <c r="P22" s="20"/>
       <c r="Q22" s="10">
         <v>30</v>
       </c>
@@ -1560,7 +1579,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="8">
         <v>302</v>
       </c>
@@ -1585,7 +1604,7 @@
       <c r="O23" s="12">
         <v>601</v>
       </c>
-      <c r="P23" s="15" t="s">
+      <c r="P23" s="20" t="s">
         <v>42</v>
       </c>
       <c r="Q23" s="11">
@@ -1596,7 +1615,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="8">
         <v>303</v>
       </c>
@@ -1621,7 +1640,7 @@
       <c r="O24" s="12">
         <v>602</v>
       </c>
-      <c r="P24" s="15"/>
+      <c r="P24" s="20"/>
       <c r="Q24" s="11">
         <v>10</v>
       </c>
@@ -1630,7 +1649,7 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="8">
         <v>304</v>
       </c>
@@ -1655,7 +1674,7 @@
       <c r="O25" s="12">
         <v>603</v>
       </c>
-      <c r="P25" s="15"/>
+      <c r="P25" s="20"/>
       <c r="Q25" s="11">
         <v>20</v>
       </c>
@@ -1670,18 +1689,18 @@
       <c r="B26" s="9">
         <v>402</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
       <c r="O26" s="12">
         <v>604</v>
       </c>
-      <c r="P26" s="15"/>
+      <c r="P26" s="20"/>
       <c r="Q26" s="11">
         <v>30</v>
       </c>
@@ -1690,7 +1709,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="13">
@@ -1703,23 +1722,23 @@
         <v>32</v>
       </c>
       <c r="F27" s="13">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G27" s="13">
         <v>10</v>
       </c>
       <c r="H27" s="13">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J27" s="13">
         <v>1001</v>
       </c>
       <c r="K27" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="13">
         <v>1002</v>
       </c>
@@ -1735,15 +1754,15 @@
       <c r="H28" s="13">
         <v>300</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="14">
         <v>1002</v>
       </c>
       <c r="K28" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="13">
         <v>1003</v>
       </c>
@@ -1759,15 +1778,152 @@
       <c r="H29" s="13">
         <v>100</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="14">
         <v>1003</v>
       </c>
       <c r="K29" t="s">
-        <v>41</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="15">
+        <v>1004</v>
+      </c>
+      <c r="C30" s="15">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30">
+        <v>50</v>
+      </c>
+      <c r="G30" s="15">
+        <v>10</v>
+      </c>
+      <c r="H30" s="15">
+        <v>500</v>
+      </c>
+      <c r="J30" s="15">
+        <v>1004</v>
+      </c>
+      <c r="K30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="15">
+        <v>1005</v>
+      </c>
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
+      </c>
+      <c r="G31" s="15">
+        <v>10</v>
+      </c>
+      <c r="J31" s="15">
+        <v>1005</v>
+      </c>
+      <c r="K31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B32" s="17">
+        <v>2001</v>
+      </c>
+      <c r="C32" s="17">
+        <v>1</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32">
+        <v>600</v>
+      </c>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17">
+        <v>600</v>
+      </c>
+      <c r="J32" s="17">
+        <v>2001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="18">
+        <v>2002</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33">
+        <v>60</v>
+      </c>
+      <c r="G33" s="18">
+        <v>10</v>
+      </c>
+      <c r="H33" s="18">
+        <v>600</v>
+      </c>
+      <c r="J33" s="18">
+        <v>2002</v>
+      </c>
+      <c r="K33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="18">
+        <v>2003</v>
+      </c>
+      <c r="C34" s="18">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
+        <v>120</v>
+      </c>
+      <c r="G34" s="18">
+        <v>5</v>
+      </c>
+      <c r="H34" s="18">
+        <v>600</v>
+      </c>
+      <c r="J34" s="18">
+        <v>2003</v>
+      </c>
+      <c r="K34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="18" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="P3:P6"/>
     <mergeCell ref="A18:A21"/>

--- a/Complete_LOG.xlsx
+++ b/Complete_LOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E398691-29E0-40B1-8168-C9D265710DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBE9B6D-DFCF-470F-B56A-E7F3D787A7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
   <si>
     <t>Training data folder</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>Material dist</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>I (Big material dist)</t>
   </si>
 </sst>
 </file>
@@ -253,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -289,6 +295,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -629,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8928FC43-EDFC-4E42-BD9C-B150B86ED97F}">
-  <dimension ref="A2:T35"/>
+  <dimension ref="A2:T37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -639,6 +648,7 @@
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="11.28515625" customWidth="1"/>
     <col min="20" max="20" width="12.28515625" customWidth="1"/>
@@ -732,7 +742,7 @@
       <c r="O3" s="2">
         <v>101</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="20" t="s">
         <v>19</v>
       </c>
       <c r="Q3" s="1">
@@ -779,7 +789,7 @@
       <c r="O4" s="2">
         <v>102</v>
       </c>
-      <c r="P4" s="19"/>
+      <c r="P4" s="20"/>
       <c r="Q4" s="1">
         <v>1.5</v>
       </c>
@@ -824,7 +834,7 @@
       <c r="O5" s="2">
         <v>103</v>
       </c>
-      <c r="P5" s="19"/>
+      <c r="P5" s="20"/>
       <c r="Q5" s="1">
         <v>2</v>
       </c>
@@ -869,7 +879,7 @@
       <c r="O6" s="2">
         <v>104</v>
       </c>
-      <c r="P6" s="19"/>
+      <c r="P6" s="20"/>
       <c r="Q6" s="1">
         <v>3</v>
       </c>
@@ -916,7 +926,7 @@
       <c r="O7" s="4">
         <v>201</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" s="20" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="1">
@@ -969,7 +979,7 @@
       <c r="O8" s="4">
         <v>202</v>
       </c>
-      <c r="P8" s="19"/>
+      <c r="P8" s="20"/>
       <c r="Q8" s="1">
         <v>20</v>
       </c>
@@ -1018,7 +1028,7 @@
       <c r="O9" s="4">
         <v>203</v>
       </c>
-      <c r="P9" s="19"/>
+      <c r="P9" s="20"/>
       <c r="Q9" s="1">
         <v>31</v>
       </c>
@@ -1067,7 +1077,7 @@
       <c r="O10" s="4">
         <v>204</v>
       </c>
-      <c r="P10" s="19"/>
+      <c r="P10" s="20"/>
       <c r="Q10" s="1">
         <v>45</v>
       </c>
@@ -1118,7 +1128,7 @@
       <c r="O11" s="4">
         <v>301</v>
       </c>
-      <c r="P11" s="19" t="s">
+      <c r="P11" s="20" t="s">
         <v>15</v>
       </c>
       <c r="Q11" s="1">
@@ -1165,7 +1175,7 @@
       <c r="O12" s="4">
         <v>302</v>
       </c>
-      <c r="P12" s="19"/>
+      <c r="P12" s="20"/>
       <c r="Q12" s="1">
         <v>20</v>
       </c>
@@ -1210,7 +1220,7 @@
       <c r="O13" s="4">
         <v>303</v>
       </c>
-      <c r="P13" s="19"/>
+      <c r="P13" s="20"/>
       <c r="Q13" s="1">
         <v>31</v>
       </c>
@@ -1255,7 +1265,7 @@
       <c r="O14" s="4">
         <v>304</v>
       </c>
-      <c r="P14" s="19"/>
+      <c r="P14" s="20"/>
       <c r="Q14" s="1">
         <v>45</v>
       </c>
@@ -1300,7 +1310,7 @@
       <c r="O15" s="2">
         <v>401</v>
       </c>
-      <c r="P15" s="19" t="s">
+      <c r="P15" s="20" t="s">
         <v>19</v>
       </c>
       <c r="Q15" s="1">
@@ -1343,7 +1353,7 @@
       <c r="O16" s="2">
         <v>402</v>
       </c>
-      <c r="P16" s="19"/>
+      <c r="P16" s="20"/>
       <c r="Q16" s="1">
         <v>1.5</v>
       </c>
@@ -1384,7 +1394,7 @@
       <c r="O17" s="2">
         <v>403</v>
       </c>
-      <c r="P17" s="19"/>
+      <c r="P17" s="20"/>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
@@ -1395,7 +1405,7 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1">
@@ -1428,7 +1438,7 @@
       <c r="O18" s="2">
         <v>404</v>
       </c>
-      <c r="P18" s="19"/>
+      <c r="P18" s="20"/>
       <c r="Q18" s="1">
         <v>3</v>
       </c>
@@ -1439,7 +1449,7 @@
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="8">
         <v>202</v>
       </c>
@@ -1464,7 +1474,7 @@
       <c r="O19" s="12">
         <v>501</v>
       </c>
-      <c r="P19" s="20" t="s">
+      <c r="P19" s="21" t="s">
         <v>43</v>
       </c>
       <c r="Q19" s="10">
@@ -1475,7 +1485,7 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="8">
         <v>203</v>
       </c>
@@ -1500,7 +1510,7 @@
       <c r="O20" s="12">
         <v>502</v>
       </c>
-      <c r="P20" s="20"/>
+      <c r="P20" s="21"/>
       <c r="Q20" s="10">
         <v>10</v>
       </c>
@@ -1509,7 +1519,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="8">
         <v>204</v>
       </c>
@@ -1534,7 +1544,7 @@
       <c r="O21" s="12">
         <v>503</v>
       </c>
-      <c r="P21" s="20"/>
+      <c r="P21" s="21"/>
       <c r="Q21" s="10">
         <v>20</v>
       </c>
@@ -1543,7 +1553,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="8">
@@ -1570,7 +1580,7 @@
       <c r="O22" s="12">
         <v>504</v>
       </c>
-      <c r="P22" s="20"/>
+      <c r="P22" s="21"/>
       <c r="Q22" s="10">
         <v>30</v>
       </c>
@@ -1579,7 +1589,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="8">
         <v>302</v>
       </c>
@@ -1604,7 +1614,7 @@
       <c r="O23" s="12">
         <v>601</v>
       </c>
-      <c r="P23" s="20" t="s">
+      <c r="P23" s="21" t="s">
         <v>42</v>
       </c>
       <c r="Q23" s="11">
@@ -1615,7 +1625,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="8">
         <v>303</v>
       </c>
@@ -1640,7 +1650,7 @@
       <c r="O24" s="12">
         <v>602</v>
       </c>
-      <c r="P24" s="20"/>
+      <c r="P24" s="21"/>
       <c r="Q24" s="11">
         <v>10</v>
       </c>
@@ -1649,7 +1659,7 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="8">
         <v>304</v>
       </c>
@@ -1674,7 +1684,7 @@
       <c r="O25" s="12">
         <v>603</v>
       </c>
-      <c r="P25" s="20"/>
+      <c r="P25" s="21"/>
       <c r="Q25" s="11">
         <v>20</v>
       </c>
@@ -1689,18 +1699,18 @@
       <c r="B26" s="9">
         <v>402</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
       <c r="O26" s="12">
         <v>604</v>
       </c>
-      <c r="P26" s="20"/>
+      <c r="P26" s="21"/>
       <c r="Q26" s="11">
         <v>30</v>
       </c>
@@ -1709,7 +1719,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="20" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="13">
@@ -1738,7 +1748,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="13">
         <v>1002</v>
       </c>
@@ -1762,7 +1772,7 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="13">
         <v>1003</v>
       </c>
@@ -1786,7 +1796,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="15">
@@ -1815,7 +1825,7 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="15">
         <v>1005</v>
       </c>
@@ -1917,8 +1927,52 @@
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="19">
+        <v>2004</v>
+      </c>
+      <c r="C35" s="19">
+        <v>1</v>
+      </c>
       <c r="D35" s="18" t="s">
         <v>27</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35" s="19">
+        <v>60</v>
+      </c>
+      <c r="H35" s="19">
+        <v>600</v>
+      </c>
+      <c r="J35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="19">
+        <v>2005</v>
+      </c>
+      <c r="C37" s="19">
+        <v>1</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37">
+        <v>600</v>
+      </c>
+      <c r="G37" s="19">
+        <v>1</v>
+      </c>
+      <c r="H37" s="19">
+        <v>600</v>
+      </c>
+      <c r="J37" s="19">
+        <v>2005</v>
+      </c>
+      <c r="K37" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Complete_LOG.xlsx
+++ b/Complete_LOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main_IMN\MSF_IMN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBE9B6D-DFCF-470F-B56A-E7F3D787A7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF496A1-50BF-4739-A4FF-FE07045C4D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18BDFBD8-CEB9-4E01-85BC-BB613A3B208E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="50">
   <si>
     <t>Training data folder</t>
   </si>
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -322,7 +322,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8928FC43-EDFC-4E42-BD9C-B150B86ED97F}">
-  <dimension ref="A2:T37"/>
+  <dimension ref="A2:T43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -742,7 +748,7 @@
       <c r="O3" s="2">
         <v>101</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="21" t="s">
         <v>19</v>
       </c>
       <c r="Q3" s="1">
@@ -789,7 +795,7 @@
       <c r="O4" s="2">
         <v>102</v>
       </c>
-      <c r="P4" s="20"/>
+      <c r="P4" s="21"/>
       <c r="Q4" s="1">
         <v>1.5</v>
       </c>
@@ -834,7 +840,7 @@
       <c r="O5" s="2">
         <v>103</v>
       </c>
-      <c r="P5" s="20"/>
+      <c r="P5" s="21"/>
       <c r="Q5" s="1">
         <v>2</v>
       </c>
@@ -879,7 +885,7 @@
       <c r="O6" s="2">
         <v>104</v>
       </c>
-      <c r="P6" s="20"/>
+      <c r="P6" s="21"/>
       <c r="Q6" s="1">
         <v>3</v>
       </c>
@@ -926,7 +932,7 @@
       <c r="O7" s="4">
         <v>201</v>
       </c>
-      <c r="P7" s="20" t="s">
+      <c r="P7" s="21" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="1">
@@ -979,7 +985,7 @@
       <c r="O8" s="4">
         <v>202</v>
       </c>
-      <c r="P8" s="20"/>
+      <c r="P8" s="21"/>
       <c r="Q8" s="1">
         <v>20</v>
       </c>
@@ -1028,7 +1034,7 @@
       <c r="O9" s="4">
         <v>203</v>
       </c>
-      <c r="P9" s="20"/>
+      <c r="P9" s="21"/>
       <c r="Q9" s="1">
         <v>31</v>
       </c>
@@ -1077,7 +1083,7 @@
       <c r="O10" s="4">
         <v>204</v>
       </c>
-      <c r="P10" s="20"/>
+      <c r="P10" s="21"/>
       <c r="Q10" s="1">
         <v>45</v>
       </c>
@@ -1128,7 +1134,7 @@
       <c r="O11" s="4">
         <v>301</v>
       </c>
-      <c r="P11" s="20" t="s">
+      <c r="P11" s="21" t="s">
         <v>15</v>
       </c>
       <c r="Q11" s="1">
@@ -1175,7 +1181,7 @@
       <c r="O12" s="4">
         <v>302</v>
       </c>
-      <c r="P12" s="20"/>
+      <c r="P12" s="21"/>
       <c r="Q12" s="1">
         <v>20</v>
       </c>
@@ -1220,7 +1226,7 @@
       <c r="O13" s="4">
         <v>303</v>
       </c>
-      <c r="P13" s="20"/>
+      <c r="P13" s="21"/>
       <c r="Q13" s="1">
         <v>31</v>
       </c>
@@ -1265,7 +1271,7 @@
       <c r="O14" s="4">
         <v>304</v>
       </c>
-      <c r="P14" s="20"/>
+      <c r="P14" s="21"/>
       <c r="Q14" s="1">
         <v>45</v>
       </c>
@@ -1310,7 +1316,7 @@
       <c r="O15" s="2">
         <v>401</v>
       </c>
-      <c r="P15" s="20" t="s">
+      <c r="P15" s="21" t="s">
         <v>19</v>
       </c>
       <c r="Q15" s="1">
@@ -1353,7 +1359,7 @@
       <c r="O16" s="2">
         <v>402</v>
       </c>
-      <c r="P16" s="20"/>
+      <c r="P16" s="21"/>
       <c r="Q16" s="1">
         <v>1.5</v>
       </c>
@@ -1394,7 +1400,7 @@
       <c r="O17" s="2">
         <v>403</v>
       </c>
-      <c r="P17" s="20"/>
+      <c r="P17" s="21"/>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
@@ -1405,7 +1411,7 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1">
@@ -1438,7 +1444,7 @@
       <c r="O18" s="2">
         <v>404</v>
       </c>
-      <c r="P18" s="20"/>
+      <c r="P18" s="21"/>
       <c r="Q18" s="1">
         <v>3</v>
       </c>
@@ -1449,7 +1455,7 @@
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="8">
         <v>202</v>
       </c>
@@ -1474,7 +1480,7 @@
       <c r="O19" s="12">
         <v>501</v>
       </c>
-      <c r="P19" s="21" t="s">
+      <c r="P19" s="22" t="s">
         <v>43</v>
       </c>
       <c r="Q19" s="10">
@@ -1485,7 +1491,7 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="8">
         <v>203</v>
       </c>
@@ -1510,7 +1516,7 @@
       <c r="O20" s="12">
         <v>502</v>
       </c>
-      <c r="P20" s="21"/>
+      <c r="P20" s="22"/>
       <c r="Q20" s="10">
         <v>10</v>
       </c>
@@ -1519,7 +1525,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="8">
         <v>204</v>
       </c>
@@ -1544,7 +1550,7 @@
       <c r="O21" s="12">
         <v>503</v>
       </c>
-      <c r="P21" s="21"/>
+      <c r="P21" s="22"/>
       <c r="Q21" s="10">
         <v>20</v>
       </c>
@@ -1553,7 +1559,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="8">
@@ -1580,7 +1586,7 @@
       <c r="O22" s="12">
         <v>504</v>
       </c>
-      <c r="P22" s="21"/>
+      <c r="P22" s="22"/>
       <c r="Q22" s="10">
         <v>30</v>
       </c>
@@ -1589,7 +1595,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="8">
         <v>302</v>
       </c>
@@ -1614,7 +1620,7 @@
       <c r="O23" s="12">
         <v>601</v>
       </c>
-      <c r="P23" s="21" t="s">
+      <c r="P23" s="22" t="s">
         <v>42</v>
       </c>
       <c r="Q23" s="11">
@@ -1625,7 +1631,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="8">
         <v>303</v>
       </c>
@@ -1650,7 +1656,7 @@
       <c r="O24" s="12">
         <v>602</v>
       </c>
-      <c r="P24" s="21"/>
+      <c r="P24" s="22"/>
       <c r="Q24" s="11">
         <v>10</v>
       </c>
@@ -1659,7 +1665,7 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="8">
         <v>304</v>
       </c>
@@ -1684,7 +1690,7 @@
       <c r="O25" s="12">
         <v>603</v>
       </c>
-      <c r="P25" s="21"/>
+      <c r="P25" s="22"/>
       <c r="Q25" s="11">
         <v>20</v>
       </c>
@@ -1699,18 +1705,18 @@
       <c r="B26" s="9">
         <v>402</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
       <c r="O26" s="12">
         <v>604</v>
       </c>
-      <c r="P26" s="21"/>
+      <c r="P26" s="22"/>
       <c r="Q26" s="11">
         <v>30</v>
       </c>
@@ -1719,7 +1725,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="21" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="13">
@@ -1748,7 +1754,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="13">
         <v>1002</v>
       </c>
@@ -1772,7 +1778,7 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="13">
         <v>1003</v>
       </c>
@@ -1796,7 +1802,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="15">
@@ -1825,7 +1831,7 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="15">
         <v>1005</v>
       </c>
@@ -1973,6 +1979,87 @@
       </c>
       <c r="K37" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>3001</v>
+      </c>
+      <c r="C40" s="23">
+        <v>9</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="20"/>
+      <c r="F40" s="23">
+        <v>1</v>
+      </c>
+      <c r="G40" s="20">
+        <v>10</v>
+      </c>
+      <c r="H40" s="23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>3002</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>3003</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+      <c r="H42">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>3004</v>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>900</v>
       </c>
     </row>
   </sheetData>
